--- a/AAII_Financials/Yearly/SES_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SES_YR_FIN.xlsx
@@ -876,7 +876,7 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>-2100</v>
+        <v>-800</v>
       </c>
       <c r="E14" s="3">
         <v>4800</v>
@@ -1021,7 +1021,7 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>1600</v>
+        <v>300</v>
       </c>
       <c r="E20" s="3">
         <v>1000</v>
@@ -1051,7 +1051,7 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-73900</v>
+        <v>-72600</v>
       </c>
       <c r="E21" s="3">
         <v>-101900</v>
@@ -1381,7 +1381,7 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-1600</v>
+        <v>-300</v>
       </c>
       <c r="E32" s="3">
         <v>-1000</v>
